--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -1468,7 +1468,7 @@
         <v>136007932</v>
       </c>
       <c r="B9" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136007917</v>
       </c>
       <c r="B23" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135840242</v>
+        <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>83465</v>
+        <v>79555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752044</v>
+        <v>752001</v>
       </c>
       <c r="R2" t="n">
-        <v>7519557</v>
+        <v>7519490</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,69 +761,74 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Fuktig svacka med gammal gransumpskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840242</t>
+          <t>https://artportalen.se/Sighting/136868476</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135843483</v>
+        <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>92445</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752153</v>
+        <v>752034</v>
       </c>
       <c r="R3" t="n">
-        <v>7519896</v>
+        <v>7519394</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,69 +868,74 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Fuktig svacka med gammal barrsumpskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843483</t>
+          <t>https://artportalen.se/Sighting/136868475</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135843499</v>
+        <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>92315</v>
+        <v>83343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3008</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752044</v>
+        <v>752141</v>
       </c>
       <c r="R4" t="n">
-        <v>7519532</v>
+        <v>7519951</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +959,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,31 +975,36 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Senvuxen, gammal gransumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843499</t>
+          <t>https://artportalen.se/Sighting/136868500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135840237</v>
+        <v>135840242</v>
       </c>
       <c r="B5" t="n">
-        <v>92023</v>
+        <v>83465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752168</v>
+        <v>752044</v>
       </c>
       <c r="R5" t="n">
-        <v>7519543</v>
+        <v>7519557</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,38 +1107,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840237</t>
+          <t>https://artportalen.se/Sighting/135840242</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135843496</v>
+        <v>135843483</v>
       </c>
       <c r="B6" t="n">
-        <v>92229</v>
+        <v>92445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3277</v>
+        <v>2063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752095</v>
+        <v>752153</v>
       </c>
       <c r="R6" t="n">
-        <v>7519531</v>
+        <v>7519896</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,38 +1219,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843496</t>
+          <t>https://artportalen.se/Sighting/135843483</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135843498</v>
+        <v>135843499</v>
       </c>
       <c r="B7" t="n">
-        <v>92229</v>
+        <v>92315</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3277</v>
+        <v>3008</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752058</v>
+        <v>752044</v>
       </c>
       <c r="R7" t="n">
-        <v>7519508</v>
+        <v>7519532</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1310,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,16 +1331,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843498</t>
+          <t>https://artportalen.se/Sighting/135843499</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135843494</v>
+        <v>135840237</v>
       </c>
       <c r="B8" t="n">
-        <v>87496</v>
+        <v>92023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1348,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bergsmannijärvi, T lm</t>
+          <t>Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752167</v>
+        <v>752168</v>
       </c>
       <c r="R8" t="n">
-        <v>7519524</v>
+        <v>7519543</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,34 +1426,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843494</t>
+          <t>https://artportalen.se/Sighting/135840237</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136007932</v>
+        <v>135843496</v>
       </c>
       <c r="B9" t="n">
-        <v>89334</v>
+        <v>92229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,37 +1460,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4412</v>
+        <v>3277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752115</v>
+        <v>752095</v>
       </c>
       <c r="R9" t="n">
-        <v>7519834</v>
+        <v>7519531</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,22 +1514,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,27 +1544,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007932</t>
+          <t>https://artportalen.se/Sighting/135843496</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135843487</v>
+        <v>135843498</v>
       </c>
       <c r="B10" t="n">
-        <v>92767</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5454</v>
+        <v>3277</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,13 +1596,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752195</v>
+        <v>752058</v>
       </c>
       <c r="R10" t="n">
-        <v>7519938</v>
+        <v>7519508</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,16 +1667,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843487</t>
+          <t>https://artportalen.se/Sighting/135843498</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135840201</v>
+        <v>135843494</v>
       </c>
       <c r="B11" t="n">
-        <v>78876</v>
+        <v>87496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,37 +1684,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752073</v>
+        <v>752167</v>
       </c>
       <c r="R11" t="n">
-        <v>7519813</v>
+        <v>7519524</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1759,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,33 +1762,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840201</t>
+          <t>https://artportalen.se/Sighting/135843494</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135840206</v>
+        <v>136007932</v>
       </c>
       <c r="B12" t="n">
-        <v>78876</v>
+        <v>89334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,37 +1797,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>bergmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752102</v>
+        <v>752115</v>
       </c>
       <c r="R12" t="n">
-        <v>7519878</v>
+        <v>7519834</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,22 +1851,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,22 +1886,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840206</t>
+          <t>https://artportalen.se/Sighting/136007932</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135840203</v>
+        <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>79230</v>
+        <v>89338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,37 +1909,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752097</v>
+        <v>751931</v>
       </c>
       <c r="R13" t="n">
-        <v>7519837</v>
+        <v>7519953</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1978,22 +1963,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2004,31 +1979,36 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med björkinslag på blåbärsris</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840203</t>
+          <t>https://artportalen.se/Sighting/136868504</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135840204</v>
+        <v>135843487</v>
       </c>
       <c r="B14" t="n">
-        <v>80092</v>
+        <v>92767</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,37 +2016,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Bergsmannijärvi, T lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752089</v>
+        <v>752195</v>
       </c>
       <c r="R14" t="n">
-        <v>7519839</v>
+        <v>7519938</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2095,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2105,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,49 +2100,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>per-erik mukka, Anna Öhlund, Christina Boyd, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840204</t>
+          <t>https://artportalen.se/Sighting/135843487</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135840211</v>
+        <v>135840201</v>
       </c>
       <c r="B15" t="n">
-        <v>80482</v>
+        <v>78876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2172,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752189</v>
+        <v>752073</v>
       </c>
       <c r="R15" t="n">
-        <v>7519891</v>
+        <v>7519813</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,7 +2187,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2217,7 +2197,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,38 +2223,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840211</t>
+          <t>https://artportalen.se/Sighting/135840201</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135840213</v>
+        <v>135840206</v>
       </c>
       <c r="B16" t="n">
-        <v>80482</v>
+        <v>78876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,13 +2264,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752162</v>
+        <v>752102</v>
       </c>
       <c r="R16" t="n">
-        <v>7519893</v>
+        <v>7519878</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2319,7 +2299,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2309,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,54 +2335,54 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840213</t>
+          <t>https://artportalen.se/Sighting/135840206</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135840210</v>
+        <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>78879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752141</v>
+        <v>752238</v>
       </c>
       <c r="R17" t="n">
-        <v>7519886</v>
+        <v>7519459</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,22 +2406,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,31 +2422,36 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre tallskog med inslag av gran och björk på blåbärsris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840210</t>
+          <t>https://artportalen.se/Sighting/136868477</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135834021</v>
+        <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>58110</v>
+        <v>78879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2484,41 +2459,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752226</v>
+        <v>751944</v>
       </c>
       <c r="R18" t="n">
-        <v>7519924</v>
+        <v>7519843</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,22 +2513,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,69 +2529,74 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik tallskog med inslag av gran och björk på blåbärsris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135834021</t>
+          <t>https://artportalen.se/Sighting/136868505</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135840239</v>
+        <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>106467</v>
+        <v>83463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752120</v>
+        <v>751949</v>
       </c>
       <c r="R19" t="n">
-        <v>7519555</v>
+        <v>7519765</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,22 +2620,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,53 +2636,58 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik barrblandskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840239</t>
+          <t>https://artportalen.se/Sighting/136868506</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135840205</v>
+        <v>135840203</v>
       </c>
       <c r="B20" t="n">
-        <v>98209</v>
+        <v>79230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752084</v>
+        <v>752097</v>
       </c>
       <c r="R20" t="n">
-        <v>7519866</v>
+        <v>7519837</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,7 +2732,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2742,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,38 +2768,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840205</t>
+          <t>https://artportalen.se/Sighting/135840203</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135840240</v>
+        <v>135840204</v>
       </c>
       <c r="B21" t="n">
-        <v>98203</v>
+        <v>80092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>752042</v>
+        <v>752089</v>
       </c>
       <c r="R21" t="n">
-        <v>7519458</v>
+        <v>7519839</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2883,7 +2844,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2854,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,60 +2874,60 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840240</t>
+          <t>https://artportalen.se/Sighting/135840204</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135840225</v>
+        <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>98206</v>
+        <v>80095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergsmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>752025</v>
+        <v>752259</v>
       </c>
       <c r="R22" t="n">
-        <v>7519756</v>
+        <v>7519450</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,22 +2951,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,69 +2967,74 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre tallskog med inslag av gran och björk på blåbärsris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135840225</t>
+          <t>https://artportalen.se/Sighting/136868480</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136007917</v>
+        <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>98210</v>
+        <v>80095</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>752019</v>
+        <v>752021</v>
       </c>
       <c r="R23" t="n">
-        <v>7519745</v>
+        <v>7519999</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,22 +3058,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,69 +3074,74 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog med björkinslag på blåbärsris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136007917</t>
+          <t>https://artportalen.se/Sighting/136868502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136007924</v>
+        <v>135840211</v>
       </c>
       <c r="B24" t="n">
-        <v>79497</v>
+        <v>80482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>260591</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>bergmannivaara, T lm</t>
+          <t>Bergsmannivaara, T lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751708</v>
+        <v>752189</v>
       </c>
       <c r="R24" t="n">
-        <v>7519876</v>
+        <v>7519891</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,22 +3165,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3249,13 +3200,1346 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135840211</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135840213</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80482</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>752162</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7519893</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840213</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135840210</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>752141</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7519886</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840210</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136868478</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78480</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>752241</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7519466</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre tallskog med inslag av gran och björk på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868478</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136868507</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>751928</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7519552</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik tallskog med inslag av gran på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868507</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135834021</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58110</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>752226</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7519924</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135834021</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135840239</v>
+      </c>
+      <c r="B30" t="n">
+        <v>106467</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>752120</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7519555</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840239</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135840205</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98209</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>752084</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7519866</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Christina Boyd, Anna Öhlund, per-erik mukka, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840205</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135840240</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98203</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>752042</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7519458</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840240</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135840225</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98206</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bergsmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>752025</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7519756</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135840225</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136007917</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98210</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>752019</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7519745</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136007917</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136007924</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>bergmannivaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>751708</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7519876</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136007924</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136868508</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naturskog S om Bergsmannivaara, NV om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>751957</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7519629</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre, hänglavsrik tallskog med inslag av gran på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868508</t>
         </is>
       </c>
     </row>
@@ -3284,6 +4568,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136868507</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136868507</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136868507</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89384</v>
+        <v>89387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136868507</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89387</v>
+        <v>89392</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136868507</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
+        <v>89403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 30548-2026 artfynd.xlsx
+++ b/artfynd/A 30548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136868476</v>
       </c>
       <c r="B2" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136868475</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136868500</v>
       </c>
       <c r="B4" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>136868504</v>
       </c>
       <c r="B13" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>136868477</v>
       </c>
       <c r="B17" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>136868505</v>
       </c>
       <c r="B18" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136868506</v>
       </c>
       <c r="B19" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>136868480</v>
       </c>
       <c r="B22" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>136868502</v>
       </c>
       <c r="B23" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136868478</v>
       </c>
       <c r="B27" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>136868508</v>
       </c>
       <c r="B36" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
